--- a/ConfigWorkspace/Data/level_wave.xlsx
+++ b/ConfigWorkspace/Data/level_wave.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="15160" windowHeight="10460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>该关卡的波次id，顺序读取可重复，英文分号分隔</t>
   </si>
   <si>
-    <t>1;1</t>
+    <t>2;4</t>
   </si>
 </sst>
 </file>
@@ -1002,8 +1002,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="24.0909090909091" customWidth="1"/>
   </cols>
@@ -1071,22 +1071,36 @@
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
+      <c r="C6" s="3">
+        <v>2</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ConfigWorkspace/Data/level_wave.xlsx
+++ b/ConfigWorkspace/Data/level_wave.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -64,7 +64,10 @@
     <t>该关卡的波次id，顺序读取可重复，英文分号分隔</t>
   </si>
   <si>
-    <t>2;4</t>
+    <t>4;5</t>
+  </si>
+  <si>
+    <t>5;6</t>
   </si>
 </sst>
 </file>
@@ -1098,8 +1101,12 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="D9" s="1"/>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/level_wave.xlsx
+++ b/ConfigWorkspace/Data/level_wave.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="15160" windowHeight="10460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -64,7 +64,10 @@
     <t>该关卡的波次id，顺序读取可重复，英文分号分隔</t>
   </si>
   <si>
-    <t>1;1</t>
+    <t>4;5</t>
+  </si>
+  <si>
+    <t>5;6</t>
   </si>
 </sst>
 </file>
@@ -1002,8 +1005,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="24.0909090909091" customWidth="1"/>
   </cols>
@@ -1071,22 +1074,40 @@
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
+      <c r="C6" s="3">
+        <v>2</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ConfigWorkspace/Data/level_wave.xlsx
+++ b/ConfigWorkspace/Data/level_wave.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>5;6</t>
+  </si>
+  <si>
+    <t>7;8;9</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1008,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="24.0909090909091" customWidth="1"/>
@@ -1108,6 +1111,14 @@
         <v>12</v>
       </c>
       <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ConfigWorkspace/Data/level_wave.xlsx
+++ b/ConfigWorkspace/Data/level_wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD88517-6601-4A52-80FF-62CFC00EE0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC38482-0C4D-4817-A141-63AB9A89D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6135" yWindow="9855" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -99,13 +99,17 @@
   </si>
   <si>
     <t>describe</t>
+  </si>
+  <si>
+    <t>教学关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +120,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -142,7 +154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -154,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -422,15 +437,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="48.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -444,7 +459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -458,7 +473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -472,7 +487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -486,75 +501,86 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B6" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B8" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+    <row r="9" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="B9" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B10" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -565,7 +591,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ConfigWorkspace/Data/level_wave.xlsx
+++ b/ConfigWorkspace/Data/level_wave.xlsx
@@ -1,140 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC38482-0C4D-4817-A141-63AB9A89D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6135" yWindow="9855" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6135" yWindow="9855" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>wave_ids</t>
-  </si>
-  <si>
-    <t>关卡名称与核心体验</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>(list#sep=;),int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>关卡ID</t>
-  </si>
-  <si>
-    <t>该关卡的波次id，顺序读取可重复，英文分号分隔</t>
-  </si>
-  <si>
-    <t>1;2</t>
-  </si>
-  <si>
-    <t>第一关：荒原破晓（白昼，2波单点反应）</t>
-  </si>
-  <si>
-    <t>3;4;5</t>
-  </si>
-  <si>
-    <t>第二关：夕照残垣（白昼 → 黄昏，3波陶砖防线）</t>
-  </si>
-  <si>
-    <t>6;7;8</t>
-  </si>
-  <si>
-    <t>第三关：雷暴前夜（黄昏，3波草丛大火+精英种子）</t>
-  </si>
-  <si>
-    <t>9;10;11</t>
-  </si>
-  <si>
-    <t>第四关：极暗蚀穴（黄昏 → 夜晚，3波入夜等离子爆轰）</t>
-  </si>
-  <si>
-    <t>12;13;14;15</t>
-  </si>
-  <si>
-    <t>第五关：永夜终局（深夜，4波全元素狂欢大暴兵）</t>
-  </si>
-  <si>
-    <t>describe</t>
-  </si>
-  <si>
-    <t>教学关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,40 +59,100 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -436,165 +405,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="48.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46" style="1" customWidth="1"/>
+    <col width="9" customWidth="1" style="2" min="1" max="2"/>
+    <col width="48.125" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="46" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>wave_ids</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>describe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>(list#sep=;),int</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>关卡ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>该关卡的波次id，顺序读取可重复，英文分号分隔</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>关卡名称与核心体验</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>教学关</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1;2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>第一关：沉沙水渠（2 波次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3;4;5</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>第二关：熔渣窑炉（3 波次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6;7;8;9</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>第三关：逆生温室（4 波次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1" s="5">
+      <c r="B9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10;11;12;13</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>第四关：极地电站（4 波次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B7" s="2">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="27" x14ac:dyDescent="0.15">
-      <c r="B9" s="2">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B10" s="2">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="C11" s="2"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14;15;16;17;18;19;20</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>第五关：永夜核心（7 波次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="2" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>